--- a/medford_endoskopy.xlsx
+++ b/medford_endoskopy.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Aohua, Pentax, SonoScape, Olympus, GE — всего 20 позиций.</t>
+          <t>Эндоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Aohua, Pentax, SonoScape, Olympus, GE.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_endoskopy.xlsx
+++ b/medford_endoskopy.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать эндоскопы для клиники?</t>
+          <t>Что такое гибкий эндоскоп?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Диаметр вводимой трубки, мм, Рабочая длина, мм, Угол поля зрения, °, Глубина резкости, мм). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Гибкий эндоскоп — медицинский прибор с подвижной вводимой трубкой и управляемым дистальным концом для осмотра полых органов через естественные пути. Видеоэндоскоп передаёт изображение с матрицы на дистальном конце на видеопроцессор и монитор. Через инструментальный канал выполняют биопсию, аспирацию и лечебные манипуляции.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем гастроскоп отличается от колоноскопа?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Гастроскоп предназначен для пищевода, желудка и двенадцатиперстной кишки: диаметр около 5,6–9,6 мм, рабочая длина 620–1050 мм. Колоноскоп рассчитан на толстую кишку и длиннее — 1650–1700 мм при диаметре 12–12,8 мм. Это разные приборы, взаимозаменять их нельзя из-за длины и жёсткости трубки.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Какой эндоскоп нужен для бронхов?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Aohua, Pentax, SonoScape, Olympus, GE. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Для трахеи и бронхов применяют бронхоскоп с тонкой трубкой 5–6 мм и рабочей длиной около 600 мм, например Olympus BF-1TQ170 (диаметр дистального конца 5,9 мм) или Huger FB-53A (5,0 мм). Тонкий диаметр позволяет проходить в долевые и сегментарные бронхи с меньшей травматичностью.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Что такое ультразвуковой эндоскоп?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Ультразвуковой эндоскоп сочетает оптику с ультразвуковым датчиком на дистальном конце и позволяет исследовать стенку ЖКТ и прилежащие структуры изнутри (эндо-УЗИ). Бывает радиальным (EG-UR5) и конвексным (EG-UC5T с каналом 4 мм для пункции под контролем). Применяется там, где обычной оптики недостаточно.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Какой диаметр инструментального канала выбрать?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Диаметр канала выбирают под планируемые инструменты и манипуляции: для диагностической биопсии достаточно стандартного канала, для лечебных вмешательств и пункций под УЗ-контролем нужен более широкий (например, 4 мм у EG-UC5T). Сначала определяют список процедур, затем подбирают канал, а не наоборот.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоят эндоскопы?</t>
+          <t>Совместим ли эндоскоп с моей стойкой?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Совместимость определяется брендом и линейкой видеопроцессора, типом разъёма и протоколом передачи изображения. Эндоскоп одного производителя, как правило, работает со своей серией процессоров; кросс-совместимость с другими брендами ограничена. Модель процессора и источника света сверяют до заказа эндоскопа.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит сделать эндоскопию желудка?</t>
+          <t>Нужна ли регистрация Росздравнадзора?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Для клинического использования эндоскоп должен быть зарегистрированным медицинским изделием с действующим регистрационным удостоверением Росздравнадзора. Технические и бытовые (USB, автомобильные) эндоскопы к медицинскому применению не допускаются. Наличие и статус РУ уточняют до покупки, это условие законной эксплуатации в клинике.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1264,6 +1264,44 @@
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_08</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Сколько служит гибкий эндоскоп?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Срок службы зависит от интенсивности использования, аккуратности обработки и своевременного сервиса. Наиболее уязвимы вводимая трубка, изгибаемая часть и инструментальный канал. Продлевает ресурс корректная дезинфекция по инструкции, хранение в вертикальном шкафу и плановое обслуживание с заменой изнашиваемых узлов.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>endoskopy</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2186,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Aohua, Pentax, SonoScape, Olympus, GE.</t>
+          <t>Эндоскопы гибкие — приборы для визуального осмотра полых органов через естественные пути или проколы. В категории собраны видеогастроскопы, видеоколоноскопы, бронхоскопы, риноларингоскопы, дуоденоскопы, холедохоскопы и ультразвуковые эндоскопы брендов Olympus, Pentax, SonoScape, Aohua и Huger. Диаметр вводимой трубки в линейке варьируется от 2,6 мм у риноларингоскопа Olympus ENF-V3 до 12,8 мм у колоноскопа Aohua HD-CL1IL, рабочая длина — от 300 до 1700 мм. Угол поля зрения моделей — 90–145°, глубина резкости — от 2 до 100 мм.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2470,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Типы гибких эндоскопов по зоне исследования</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2758,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое эндоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4642,251 +4680,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Типы гибких эндоскопов по зоне исследования</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Зона исследования</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Диаметр вводимой трубки, мм</t>
+          <t>Диаметр вводимой трубки</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Рабочая длина, мм</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Угол поля зрения, °</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Глубина резкости, мм</t>
+          <t>Рабочая длина</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Видеоколоноскоп Aohua HD-CL1IL</t>
+          <t>Гастроскоп</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Aohua</t>
+          <t>пищевод, желудок, ДПК</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>12,8</t>
+          <t>5,6–9,6 мм</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>2-100</t>
+          <t>620–1050 мм</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Видеогастроскоп Pentax EG29-V10c</t>
+          <t>Колоноскоп</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Pentax</t>
+          <t>толстая кишка</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>9,6</t>
+          <t>12,0–12,8 мм</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>140°</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>3-100</t>
+          <t>1650–1700 мм</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Видеогастроскоп SonoScape EG-500</t>
+          <t>Бронхоскоп</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>трахея, бронхи</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>9,3</t>
+          <t>5,0–6,0 мм</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>3-100</t>
+          <t>600 мм</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Видеоколоноскоп Aohua FHD-CL200JL</t>
+          <t>Риноларингоскоп</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Aohua</t>
+          <t>полость носа, гортань</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>12,8</t>
+          <t>2,6–5,8 мм</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>3-100</t>
+          <t>300–600 мм</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Видеоларингоскоп Aohua MBC-6</t>
+          <t>Холедохоскоп</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Aohua</t>
+          <t>жёлчные протоки</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>4,9 мм</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>3-50</t>
+          <t>350 мм</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Видеогастроскоп SonoScape EG-430</t>
+          <t>Ультразвуковой эндоскоп</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SonoScape</t>
+          <t>эндо-УЗИ стенки ЖКТ</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>9,3</t>
+          <t>канал 4 мм</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>140°</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>3-100</t>
+          <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4898,7 +4864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5224,12 +5190,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Определите зону исследования</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается эндоскопы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала фиксируют орган и вид процедуры: желудок и пищевод — гастроскоп, толстая кишка — колоноскоп, трахея и бронхи — бронхоскоп, нос и гортань — риноларингоскоп, жёлчные протоки — холедохоскоп. От зоны зависят диаметр, длина и жёсткость трубки, поэтому выбор начинают именно с неё, а не с марки.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5269,12 +5235,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Проверьте диаметр вводимой трубки</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Диаметр определяет проходимость и переносимость. У тонких риноларингоскопов он от 2,6 мм, у гастроскопов — около 5,6–9,6 мм, у колоноскопов — 12–12,8 мм. Для педиатрии и сложной анатомии берут более тонкие модели, для взрослой рутинной эндоскопии — стандартные диаметры с полноразмерным каналом.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5314,12 +5280,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Учтите рабочую длину</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Диаметр вводимой трубки, мм, Рабочая длина, мм, Угол поля зрения, °, Глубина резкости, мм. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Рабочая длина должна доставать до целевого отдела: гастроскопы — 620–1050 мм, колоноскопы — 1650–1700 мм, бронхоскопы и риноларингоскопы — 300–600 мм. Слишком короткий эндоскоп не достигнет зоны интереса, избыточно длинный усложняет управление, поэтому длину сверяют с протоколом исследования.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5359,12 +5325,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените инструментальный канал</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Aohua, Pentax, SonoScape, Olympus, GE.</t>
+          <t>Диаметр канала задаёт, какие инструменты пройдут: биопсийные щипцы, петли, аспирация. У ультразвукового конвексного эндоскопа EG-UC5T канал 4 мм. Если планируется биопсия или лечебные манипуляции, канал подбирают под конкретный инструментарий заранее, а не по остаточному принципу.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5404,12 +5370,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Сверьте совместимость со стойкой</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Эндоскоп работает в паре с видеопроцессором и источником света. Разъём, тип матрицы и протокол изображения должны совпадать с имеющейся стойкой того же бренда или совместимой линейки. Совместимость уточняют по модели процессора до заказа, иначе прибор не даст изображения.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5449,12 +5415,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните регистрацию и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Для клинического применения нужен зарегистрированный медизделие с действующим РУ Росздравнадзора. Заранее уточняют условия гарантии, наличие подменного фонда на время ремонта и доступность оригинальных запчастей — от этого зависит непрерывность работы кабинета.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5504,7 +5470,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Aohua, Pentax, SonoScape, Olympus, GE. При выборе обращают внимание на диаметр вводимой трубки, рабочая длина, угол поля зрения, глубина резкости, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Гибкий эндоскоп подбирают не по бренду, а по анатомической зоне и задачам кабинета. Диаметр вводимой трубки и рабочая длина должны соответствовать исследуемому органу, а диаметр инструментального канала — планируемым манипуляциям и биопсийным щипцам. Совместимость эндоскопа с видеопроцессором и источником света стоит проверять до покупки: разъём и протокол передачи должны совпадать с уже установленной стойкой.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5788,13 +5754,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое эндоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Эндоскопы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Aohua, Pentax, SonoScape, Olympus, GE. Подберём вариант под задачи вашего отделения.</t>
+          <t>Гибкий эндоскоп — медицинский прибор с управляемой вводимой трубкой для осмотра ЖКТ, дыхательных путей и ЛОР-органов. Тип выбирают по зоне исследования: для желудка нужен гастроскоп (диаметр около 9 мм, длина 1030–1050 мм), для толстой кишки — колоноскоп (12–12,8 мм, до 1700 мм), для бронхов — бронхоскоп (5–6 мм), для гортани — риноларингоскоп (2,6–5,8 мм). Ключевые параметры подбора — диаметр трубки, рабочая длина, угол поля зрения и диаметр инструментального канала под планируемые манипуляции.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5831,13 +5797,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Гибкие эндоскопы: назначение</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Диаметр вводимой трубки, мм, Рабочая длина, мм, Угол поля зрения, °, Глубина резкости, мм), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Гибкие эндоскопы применяют для прямой визуализации полых органов и полостей: желудочно-кишечного тракта, дыхательных путей, ЛОР-органов, жёлчных протоков. Управляемый дистальный конец и инструментальный канал позволяют не только осматривать слизистую, но и брать биопсию, удалять инородные тела и выполнять лечебные манипуляции без открытого доступа.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5874,13 +5840,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Типы гибких эндоскопов</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>По зоне исследования различают гастроскопы, колоноскопы, бронхоскопы, риноларингоскопы, дуоденоскопы и холедохоскопы, а также ультразвуковые эндоскопы для эндо-УЗИ. Модели отличаются диаметром вводимой трубки (от 2,6 до 12,8 мм), рабочей длиной (300–1700 мм) и диаметром инструментального канала. Тип прибора выбирают по органу и протоколу.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5917,13 +5883,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Ключевые характеристики при выборе</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>При подборе гибкого эндоскопа сравнивают диаметр дистального конца и вводимой трубки, рабочую длину, угол поля зрения (90–145°), глубину резкости (от 2 до 100 мм) и диаметр инструментального канала. Отдельно проверяют совместимость с видеопроцессором и источником света, тип оптики chip-on-the-tip и наличие регистрационного удостоверения.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5940,6 +5906,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Бренды в категории</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>В категории представлены эндоскопы Olympus, Pentax, SonoScape, Aohua и Huger. Японские Olympus и Pentax закрывают премиальный и ЛОР-сегмент с ультратонкими моделями, SonoScape и Aohua предлагают линейки гастро- и колоноскопов, включая Full HD. Подбор бренда согласуют с имеющейся стойкой, чтобы сохранить совместимость по разъёму и процессору.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>endoskopy</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
